--- a/ltt/StructureDefinition-klgateway-ltt-citizen.xlsx
+++ b/ltt/StructureDefinition-klgateway-ltt-citizen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3269" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3269" uniqueCount="591">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-31T13:04:54+02:00</t>
+    <t>2025-10-29T22:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1788,6 +1788,9 @@
   </si>
   <si>
     <t>Patient.managingOrganization.type</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Patient.managingOrganization.identifier</t>
@@ -11424,7 +11427,7 @@
         <v>540</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>541</v>
+        <v>568</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>19</v>
@@ -11474,10 +11477,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11591,10 +11594,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11708,10 +11711,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11737,16 +11740,16 @@
         <v>433</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>19</v>
@@ -11795,7 +11798,7 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11810,7 +11813,7 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>175</v>
@@ -11827,10 +11830,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11942,10 +11945,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12059,10 +12062,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12178,10 +12181,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12204,16 +12207,16 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12263,7 +12266,7 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>87</v>
@@ -12287,7 +12290,7 @@
         <v>19</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>19</v>
@@ -12295,10 +12298,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12324,10 +12327,10 @@
         <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12357,10 +12360,10 @@
         <v>208</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>19</v>
@@ -12378,7 +12381,7 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>87</v>
@@ -12393,7 +12396,7 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>175</v>
